--- a/Table/UnitRandomTable.xlsx
+++ b/Table/UnitRandomTable.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,27 +204,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>HeadAnim-string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BodyAnim-string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2/3/4/5/6/7/8/9/10/11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14/15/16/17/18/19/20/21/22/23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2/3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4/5</t>
+    <t>1/2/3/4/5/6/7/8/9/10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Face-string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/2/3/4/5/6/7/8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0/1/2/3/4/5/6/7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeadLib-string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BodyLib-string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -285,24 +297,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -616,7 +628,7 @@
     <col min="2" max="2" width="28.375" style="3" customWidth="1"/>
     <col min="3" max="3" width="12.875" style="3" customWidth="1"/>
     <col min="4" max="4" width="19.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="25.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24" style="3" customWidth="1"/>
     <col min="6" max="11" width="19.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="8.875" customWidth="1"/>
     <col min="13" max="13" width="9" customWidth="1"/>
@@ -635,28 +647,30 @@
       <c r="D1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="J1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -672,25 +686,28 @@
       <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="3">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="E2" s="5">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="6">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6">
         <v>0</v>
       </c>
-      <c r="H2" s="3">
+      <c r="I2" s="6">
         <v>0</v>
       </c>
-      <c r="I2" s="6">
+      <c r="J2" s="6">
         <v>1</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="K2" s="3">
+      <c r="K2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -707,25 +724,28 @@
       <c r="D3" s="3">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="3">
+      <c r="I3" s="6">
         <v>0</v>
       </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="10" t="s">
+      <c r="J3" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="9">
-        <v>7</v>
-      </c>
-      <c r="K3" s="3">
+      <c r="K3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="6">
         <v>1</v>
       </c>
     </row>
@@ -742,25 +762,28 @@
       <c r="D4" s="3">
         <v>13</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="3">
+      <c r="I4" s="6">
         <v>0</v>
       </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>6</v>
-      </c>
-      <c r="J4" s="3">
-        <v>8</v>
-      </c>
-      <c r="K4" s="3">
+      <c r="J4" s="6">
+        <v>1</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" s="6">
         <v>2</v>
       </c>
     </row>
@@ -768,6 +791,9 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="J3" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -833,10 +859,10 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="9" t="s">
         <v>36</v>
       </c>
     </row>
@@ -847,10 +873,10 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -859,10 +885,10 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="10"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -871,10 +897,10 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -883,10 +909,10 @@
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="10"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -895,10 +921,10 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="10"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -907,20 +933,20 @@
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="10"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -932,9 +958,9 @@
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>

--- a/Table/UnitRandomTable.xlsx
+++ b/Table/UnitRandomTable.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -224,10 +224,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0/1/2/3/4/5/6/7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -237,6 +233,14 @@
   </si>
   <si>
     <t>BodyLib-string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/2/3/4/5/6/7/8/9/10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -283,7 +287,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -309,6 +313,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -621,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" style="3" customWidth="1"/>
@@ -663,10 +670,10 @@
         <v>20</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>22</v>
@@ -689,11 +696,11 @@
       <c r="E2" s="5">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="6">
-        <v>1</v>
+      <c r="F2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="H2" s="6">
         <v>0</v>
@@ -702,10 +709,10 @@
         <v>0</v>
       </c>
       <c r="J2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L2" s="6">
         <v>0</v>
@@ -739,11 +746,11 @@
       <c r="I3" s="6">
         <v>0</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="7">
+        <v>0</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>51</v>
       </c>
       <c r="L3" s="6">
         <v>1</v>
@@ -778,21 +785,24 @@
         <v>0</v>
       </c>
       <c r="J4" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L4" s="6">
         <v>2</v>
       </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F7" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="J3" numberStoredAsText="1"/>
+    <ignoredError sqref="E4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -862,7 +872,7 @@
       <c r="C4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>36</v>
       </c>
     </row>
@@ -876,7 +886,7 @@
       <c r="C5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="10"/>
+      <c r="D5" s="11"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -888,7 +898,7 @@
       <c r="C6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="10"/>
+      <c r="D6" s="11"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -900,7 +910,7 @@
       <c r="C7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="10"/>
+      <c r="D7" s="11"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -912,7 +922,7 @@
       <c r="C8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="10"/>
+      <c r="D8" s="11"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -924,7 +934,7 @@
       <c r="C9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="10"/>
+      <c r="D9" s="11"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -936,17 +946,17 @@
       <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="11"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -958,9 +968,9 @@
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
